--- a/bin/Debug/Template/SparePartRequestSheetIPO.xlsx
+++ b/bin/Debug/Template/SparePartRequestSheetIPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT-Project\MC-Dept-App\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4864E172-EC38-4511-8412-EE9029C71A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990D04FE-AC4E-4A99-81B4-2649B36F474A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BBFB412F-6E2A-4F5D-8DDF-BCB1C8845C69}"/>
   </bookViews>
@@ -165,7 +165,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -188,12 +188,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -201,24 +238,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -229,10 +248,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -248,9 +291,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -258,801 +298,7 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="mmm\-yy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1423,25 +669,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78277B55-40C9-44DD-9957-331E1E3EEEEF}" name="PrintForm" displayName="PrintForm" ref="A3:J4" insertRow="1" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="22" tableBorderDxfId="21">
-  <autoFilter ref="A3:J4" xr:uid="{82AADA1B-A3F6-4D5A-9B6D-24C3D1153767}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F252EC0F-AA97-46A5-84A8-11D8474EEEBF}" name="Code" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{1164D89B-C5E9-49D4-BC69-EFED51D5606F}" name="Part Number" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{512A3FEF-9335-4251-90FE-39A702AD8547}" name="Part Name" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{2B65F916-A3FB-4E7C-A6CF-9E39B12D591A}" name="Machine Name" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{97D271A3-F359-4954-AD16-22CA66208BE5}" name="Supplier" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{245AA6F7-F3DA-4E23-ABB5-96CFC00A7EE4}" name="Maker" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{62E00F1B-299D-474C-BF74-367D6115D293}" name="Qty" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{E0ABF327-44D9-4CAA-BA48-9A2CEDF273E5}" name="Unit Price" dataDxfId="6" totalsRowDxfId="5" dataCellStyle="Currency"/>
-    <tableColumn id="10" xr3:uid="{65840F35-6DB8-417A-8061-0540AB30AEEE}" name="Amount" dataDxfId="4" totalsRowDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{45E8E37F-A983-4B83-8BD0-97CD2AA7E98A}" name="New Unit Price" dataDxfId="2" totalsRowDxfId="1"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1759,134 +986,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="12"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="14"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19">
-        <f>SUM(PrintForm[Amount])</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="18"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="10"/>
-      <c r="I7" s="10"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="9"/>
-      <c r="I9" s="10"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="3"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1922,8 +1146,5 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="62" fitToHeight="0" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/bin/Debug/Template/SparePartRequestSheetIPO.xlsx
+++ b/bin/Debug/Template/SparePartRequestSheetIPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT-Project\MC-Dept-App\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990D04FE-AC4E-4A99-81B4-2649B36F474A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D48CBE-18B0-434A-AAF4-DFCAD5B4AC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BBFB412F-6E2A-4F5D-8DDF-BCB1C8845C69}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -245,16 +245,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -276,6 +267,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -982,22 +983,22 @@
     <col min="7" max="7" width="10.140625" customWidth="1"/>
     <col min="8" max="8" width="15.85546875" customWidth="1"/>
     <col min="9" max="9" width="15.140625" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
@@ -1011,106 +1012,106 @@
       <c r="I2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="6"/>
+      <c r="J2" s="17"/>
     </row>
     <row r="3" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="7"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
       <c r="G9" s="3"/>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
     </row>
     <row r="12" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
